--- a/docs/private/ПВ-Система_прайс_расчет_стоимости_240000.xlsx
+++ b/docs/private/ПВ-Система_прайс_расчет_стоимости_240000.xlsx
@@ -154,7 +154,7 @@
     <t>Формула расчёта</t>
   </si>
   <si>
-    <t>Стоимость = Базовая стоимость × Kпр × Kсл  +  Доп. рабочие места × 240 000 ₽</t>
+    <t>Стоимость = Базовая стоимость × Kпр × Kсл × Количество рабочих мест</t>
   </si>
   <si>
     <t>•  Базовая стоимость — 240 000 ₽ (лицензия на 1 рабочее место, сеть горных выработок до 50 км, категория сложности I).</t>
@@ -166,7 +166,7 @@
     <t>•  Kсл — коэффициент сложности вентиляционной сети (таблица 2).</t>
   </si>
   <si>
-    <t>•  Доп. рабочие места — рабочие места сверх одного, входящего в базовую лицензию.</t>
+    <t>•  Количество рабочих мест — число компьютеров, на которых будет работать программа; коэффициенты применяются к каждому рабочему месту.</t>
   </si>
   <si>
     <t>Таблица 1. Коэффициент протяжённости сети горных выработок (Kпр)</t>
@@ -337,13 +337,13 @@
     <t>Коэффициент сложности Kсл</t>
   </si>
   <si>
-    <t>Стоимость лицензии на сеть  (база × Kпр × Kсл)</t>
+    <t>Стоимость одного рабочего места (база × Kпр × Kсл)</t>
   </si>
   <si>
     <t>Дополнительные рабочие места сверх 1</t>
   </si>
   <si>
-    <t>Стоимость доп. рабочих мест (× 240 000 ₽)</t>
+    <t>Стоимость доп. рабочих мест (× база × Kпр × Kсл)</t>
   </si>
   <si>
     <t>ИТОГО СТОИМОСТЬ ЛИЦЕНЗИИ</t>
@@ -2043,7 +2043,7 @@
         <v>106</v>
       </c>
       <c r="B19" s="36">
-        <f>B18*240000</f>
+        <f>B18*B17</f>
         <v>0</v>
       </c>
       <c r="C19" s="27"/>
@@ -2273,7 +2273,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="7">
-        <f>MAX(0,F8-1)*240000</f>
+        <f>MAX(0,F8-1)*240000*D8*E8</f>
         <v>960000</v>
       </c>
       <c r="H8" s="20">
@@ -2303,12 +2303,12 @@
         <v>5</v>
       </c>
       <c r="G9" s="10">
-        <f>MAX(0,F9-1)*240000</f>
-        <v>960000</v>
+        <f>MAX(0,F9-1)*240000*D9*E9</f>
+        <v>1497600</v>
       </c>
       <c r="H9" s="22">
         <f>240000*D9*E9+G9</f>
-        <v>1334400</v>
+        <v>1872000</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -2333,12 +2333,12 @@
         <v>8</v>
       </c>
       <c r="G10" s="7">
-        <f>MAX(0,F10-1)*240000</f>
-        <v>1680000</v>
+        <f>MAX(0,F10-1)*240000*D10*E10</f>
+        <v>3763200</v>
       </c>
       <c r="H10" s="20">
         <f>240000*D10*E10+G10</f>
-        <v>2217600</v>
+        <v>4300800</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -2363,12 +2363,12 @@
         <v>10</v>
       </c>
       <c r="G11" s="10">
-        <f>MAX(0,F11-1)*240000</f>
-        <v>2160000</v>
+        <f>MAX(0,F11-1)*240000*D11*E11</f>
+        <v>6048000</v>
       </c>
       <c r="H11" s="22">
         <f>240000*D11*E11+G11</f>
-        <v>2832000</v>
+        <v>6720000</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -2393,12 +2393,12 @@
         <v>15</v>
       </c>
       <c r="G12" s="7">
-        <f>MAX(0,F12-1)*240000</f>
-        <v>3360000</v>
+        <f>MAX(0,F12-1)*240000*D12*E12</f>
+        <v>14280000</v>
       </c>
       <c r="H12" s="20">
         <f>240000*D12*E12+G12</f>
-        <v>4380000</v>
+        <v>15300000</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">

--- a/docs/private/ПВ-Система_прайс_расчет_стоимости_240000.xlsx
+++ b/docs/private/ПВ-Система_прайс_расчет_стоимости_240000.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="147">
   <si>
     <t xml:space="preserve">      ПРАЙС-ЛИСТ НА ПРОГРАММНЫЙ КОМПЛЕКС «ПВ-СИСТЕМА»</t>
   </si>
@@ -154,7 +154,7 @@
     <t>Формула расчёта</t>
   </si>
   <si>
-    <t>Стоимость = Базовая стоимость × Kпр × Kсл × Количество рабочих мест</t>
+    <t xml:space="preserve">Стоимость = Базовая стоимость × Kпр × Kсл × Количество рабочих мест × (1 − Скидка)</t>
   </si>
   <si>
     <t>•  Базовая стоимость — 240 000 ₽ (лицензия на 1 рабочее место, сеть горных выработок до 50 км, категория сложности I).</t>
@@ -166,7 +166,7 @@
     <t>•  Kсл — коэффициент сложности вентиляционной сети (таблица 2).</t>
   </si>
   <si>
-    <t>•  Количество рабочих мест — число компьютеров, на которых будет работать программа; коэффициенты применяются к каждому рабочему месту.</t>
+    <t xml:space="preserve">•  Количество рабочих мест — число компьютеров, на которых будет работать программа; Скидка — по количеству рабочих мест (таблица 3).</t>
   </si>
   <si>
     <t>Таблица 1. Коэффициент протяжённости сети горных выработок (Kпр)</t>
@@ -379,7 +379,7 @@
     <t>Рабочих мест</t>
   </si>
   <si>
-    <t>Доп. места, ₽</t>
+    <t xml:space="preserve">Скидка за места</t>
   </si>
   <si>
     <t>Итого, ₽</t>
@@ -394,16 +394,16 @@
     <t>Сравнение: стандартные позиции прайс-листа</t>
   </si>
   <si>
-    <t>Вариант</t>
-  </si>
-  <si>
-    <t>Цена за место, ₽</t>
-  </si>
-  <si>
-    <t>Лицензионный ключ на одно рабочее место</t>
-  </si>
-  <si>
-    <t>Лицензии на 5 рабочих мест (5 × 240 000 ₽)</t>
+    <t xml:space="preserve">Вариант (без коэффициентов, сеть до 50 км, категория I)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цена за место со скидкой, ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лицензия на 1 рабочее место</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лицензии на 5 рабочих мест</t>
   </si>
   <si>
     <t>Примеры приведены для иллюстрации методики и не являются публичной офертой.</t>
@@ -413,6 +413,57 @@
   </si>
   <si>
     <t>Проектирование вентиляции и водоснабжения рудников</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таблица 3. Скидка за количество рабочих мест</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Количество рабочих мест</t>
+  </si>
+  <si>
+    <t xml:space="preserve">От, мест</t>
+  </si>
+  <si>
+    <t xml:space="preserve">До, мест</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Скидка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стандартная цена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10–14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Крупное предприятие</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 и более</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Горно-обогатительный комбинат, группа рудников</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Количество рабочих мест</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стоимость без скидки (стоимость места × количество мест)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Скидка за количество мест (табл. 3 методики)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лицензии на 10 рабочих мест (скидка 10%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лицензии на 15 рабочих мест (скидка 20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Скидка за количество рабочих мест: от 10 мест — 10%, от 15 мест — 20% (см. «Методика расчёта», табл. 3).</t>
   </si>
 </sst>
 </file>
@@ -600,7 +651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -715,6 +766,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1174,7 +1234,7 @@
     <tabColor rgb="FF0E63B0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -1467,29 +1527,36 @@
       <c r="D30" s="24"/>
       <c r="E30" s="24"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
+    <row r="31" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="31"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
       <c r="E33" s="31"/>
     </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+    </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A33:E33"/>
+  <mergeCells count="23">
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="A32:E32"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B23:E23"/>
@@ -1509,6 +1576,9 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1523,7 +1593,7 @@
     <tabColor rgb="FF0E63B0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1831,27 +1901,103 @@
       <c r="D28" s="24"/>
       <c r="E28" s="24"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
+    <row r="30" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+    </row>
+    <row r="31" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6">
+        <v>9</v>
+      </c>
+      <c r="E32" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="9">
+        <v>10</v>
+      </c>
+      <c r="D33" s="9">
+        <v>14</v>
+      </c>
+      <c r="E33" s="48">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" s="6">
+        <v>15</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="47">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="30" t="s">
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A31:E31"/>
+  <mergeCells count="14">
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
@@ -1859,11 +2005,13 @@
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -1877,7 +2025,7 @@
     <tabColor rgb="FFF2B705"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -2029,105 +2177,117 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="B18" s="42">
-        <f>MAX(0,B10-1)</f>
-        <v>0</v>
+        <f>B10</f>
+        <v>1</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="B19" s="36">
-        <f>B18*B17</f>
-        <v>0</v>
+        <f>B17*B18</f>
+        <v>240000</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
     </row>
-    <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="49">
+        <f>LOOKUP(B10,'Методика расчёта'!$C$32:$C$34,'Методика расчёта'!$E$32:$E$34)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+    </row>
+    <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B20" s="44">
-        <f>B17+B19</f>
+      <c r="B21" s="44">
+        <f>B19*(1-B20)</f>
         <v>240000</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B21" s="36">
-        <f>B20/MAX(1,B10)</f>
-        <v>240000</v>
-      </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B22" s="41" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="B22" s="36">
+        <f>B21/MAX(1,B10)</f>
+        <v>240000</v>
       </c>
       <c r="C22" s="27"/>
       <c r="D22" s="27"/>
     </row>
-    <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="35" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+    </row>
+    <row r="25" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="31"/>
       <c r="C27" s="31"/>
       <c r="D27" s="31"/>
     </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A24:D24"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="whole" operator="greaterThanOrEqual" sqref="B10" xr:uid="{00000000-0002-0000-0200-000001000000}">
@@ -2158,7 +2318,7 @@
     <tabColor rgb="FF0E63B0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2272,12 +2432,12 @@
       <c r="F8" s="19">
         <v>5</v>
       </c>
-      <c r="G8" s="7">
-        <f>MAX(0,F8-1)*240000*D8*E8</f>
-        <v>960000</v>
+      <c r="G8" s="47">
+        <f>LOOKUP(F8,'Методика расчёта'!$C$32:$C$34,'Методика расчёта'!$E$32:$E$34)</f>
+        <v>0</v>
       </c>
       <c r="H8" s="20">
-        <f>240000*D8*E8+G8</f>
+        <f>240000*D8*E8*F8*(1-G8)</f>
         <v>1200000</v>
       </c>
     </row>
@@ -2302,12 +2462,12 @@
       <c r="F9" s="21">
         <v>5</v>
       </c>
-      <c r="G9" s="10">
-        <f>MAX(0,F9-1)*240000*D9*E9</f>
-        <v>1497600</v>
+      <c r="G9" s="48">
+        <f>LOOKUP(F9,'Методика расчёта'!$C$32:$C$34,'Методика расчёта'!$E$32:$E$34)</f>
+        <v>0</v>
       </c>
       <c r="H9" s="22">
-        <f>240000*D9*E9+G9</f>
+        <f>240000*D9*E9*F9*(1-G9)</f>
         <v>1872000</v>
       </c>
     </row>
@@ -2332,12 +2492,12 @@
       <c r="F10" s="19">
         <v>8</v>
       </c>
-      <c r="G10" s="7">
-        <f>MAX(0,F10-1)*240000*D10*E10</f>
-        <v>3763200</v>
+      <c r="G10" s="47">
+        <f>LOOKUP(F10,'Методика расчёта'!$C$32:$C$34,'Методика расчёта'!$E$32:$E$34)</f>
+        <v>0</v>
       </c>
       <c r="H10" s="20">
-        <f>240000*D10*E10+G10</f>
+        <f>240000*D10*E10*F10*(1-G10)</f>
         <v>4300800</v>
       </c>
     </row>
@@ -2362,13 +2522,13 @@
       <c r="F11" s="21">
         <v>10</v>
       </c>
-      <c r="G11" s="10">
-        <f>MAX(0,F11-1)*240000*D11*E11</f>
+      <c r="G11" s="48">
+        <f>LOOKUP(F11,'Методика расчёта'!$C$32:$C$34,'Методика расчёта'!$E$32:$E$34)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H11" s="22">
+        <f>240000*D11*E11*F11*(1-G11)</f>
         <v>6048000</v>
-      </c>
-      <c r="H11" s="22">
-        <f>240000*D11*E11+G11</f>
-        <v>6720000</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -2392,13 +2552,13 @@
       <c r="F12" s="19">
         <v>15</v>
       </c>
-      <c r="G12" s="7">
-        <f>MAX(0,F12-1)*240000*D12*E12</f>
-        <v>14280000</v>
+      <c r="G12" s="47">
+        <f>LOOKUP(F12,'Методика расчёта'!$C$32:$C$34,'Методика расчёта'!$E$32:$E$34)</f>
+        <v>0.2</v>
       </c>
       <c r="H12" s="20">
-        <f>240000*D12*E12+G12</f>
-        <v>15300000</v>
+        <f>240000*D12*E12*F12*(1-G12)</f>
+        <v>12240000</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2447,6 +2607,7 @@
         <v>240000</v>
       </c>
       <c r="H16" s="7">
+        <f>F16*240000*(1-LOOKUP(F16,'Методика расчёта'!$C$32:$C$34,'Методика расчёта'!$E$32:$E$34))</f>
         <v>240000</v>
       </c>
     </row>
@@ -2466,58 +2627,100 @@
         <v>240000</v>
       </c>
       <c r="H17" s="10">
-        <f>F17*240000</f>
+        <f>F17*240000*(1-LOOKUP(F17,'Методика расчёта'!$C$32:$C$34,'Методика расчёта'!$E$32:$E$34))</f>
         <v>1200000</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
+    <row r="18" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="19">
+        <v>10</v>
+      </c>
+      <c r="G18" s="7">
+        <f>H18/F18</f>
+        <v>216000</v>
+      </c>
+      <c r="H18" s="7">
+        <f>F18*240000*(1-LOOKUP(F18,'Методика расчёта'!$C$32:$C$34,'Методика расчёта'!$E$32:$E$34))</f>
+        <v>2160000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="21">
+        <v>15</v>
+      </c>
+      <c r="G19" s="10">
+        <f>H19/F19</f>
+        <v>192000</v>
+      </c>
+      <c r="H19" s="10">
+        <f>F19*240000*(1-LOOKUP(F19,'Методика расчёта'!$C$32:$C$34,'Методика расчёта'!$E$32:$E$34))</f>
+        <v>2880000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="s">
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A21:H21"/>
+  <mergeCells count="12">
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A19:H19"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A24:H24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>

--- a/docs/private/ПВ-Система_прайс_расчет_стоимости_240000.xlsx
+++ b/docs/private/ПВ-Система_прайс_расчет_стоимости_240000.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Прайс-лист" sheetId="1" r:id="rId1"/>
     <sheet name="Методика расчёта" sheetId="2" r:id="rId2"/>
     <sheet name="Калькулятор" sheetId="3" r:id="rId3"/>
+    <sheet name="Калькулятор УК" sheetId="5" r:id="rId8"/>
     <sheet name="Примеры расчёта" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="161">
   <si>
     <t xml:space="preserve">      ПРАЙС-ЛИСТ НА ПРОГРАММНЫЙ КОМПЛЕКС «ПВ-СИСТЕМА»</t>
   </si>
@@ -464,6 +465,48 @@
   </si>
   <si>
     <t xml:space="preserve">•  Скидка за количество рабочих мест: от 10 мест — 10%, от 15 мест — 20% (см. «Методика расчёта», табл. 3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лицензия для управляющей компании — без учёта протяжённости и сложности сети</t>
+  </si>
+  <si>
+    <t xml:space="preserve">по количеству мест</t>
+  </si>
+  <si>
+    <t xml:space="preserve">см. лист «Калькулятор УК»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Расчёт для управляющих компаний</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Для управляющих компаний (лицензии приобретаются для специалистов управляющей компании без привязки к конкретной сети горных выработок) коэффициенты Kпр и Kсл и скидка за количество мест не применяются:  Стоимость = 240 000 ₽ × Количество рабочих мест.  Расчёт — на листе «Калькулятор УК».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      КАЛЬКУЛЯТОР ДЛЯ УПРАВЛЯЮЩИХ КОМПАНИЙ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Без учёта протяжённости и сложности сети · заполните поля, выделенные жёлтым</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Исходные данные управляющей компании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наименование управляющей компании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Управляющая компания (пример)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Компьютеры специалистов УК, на которых будет работать программа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стоимость лицензии на одно рабочее место</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Количество рабочих мест</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Расчёт для управляющих компаний выполняется без коэффициентов протяжённости сети горных выработок и сложности вентиляционной сети. Окончательная стоимость фиксируется в коммерческом предложении и лицензионном договоре.</t>
   </si>
 </sst>
 </file>
@@ -923,6 +966,44 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="419100" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1429,6 +1510,23 @@
         <v>26</v>
       </c>
     </row>
+    <row r="19" spans="1:5" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" s="7">
+        <v>240000</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
     <row r="20" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>27</v>
@@ -1593,7 +1691,7 @@
     <tabColor rgb="FF0E63B0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1978,26 +2076,44 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="30" t="s">
+    <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+    </row>
+    <row r="37" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="30" t="s">
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
@@ -2012,6 +2128,8 @@
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A40:E40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -2726,4 +2844,187 @@
   <pageSetup fitToHeight="0" orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFF2B705"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="4" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+    </row>
+    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+    </row>
+    <row r="4" spans="1:4" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+    </row>
+    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="24"/>
+    </row>
+    <row r="8" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="17">
+        <v>5</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="24"/>
+    </row>
+    <row r="10" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+    </row>
+    <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="38"/>
+      <c r="D11" s="39"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="36">
+        <v>240000</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="42">
+        <f>B8</f>
+        <v>5</v>
+      </c>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="44">
+        <f>B12*B13</f>
+        <v>1200000</v>
+      </c>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+    </row>
+    <row r="17" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A20:D20"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="Введите целое число не меньше 1" sqref="B8">
+      <formula1>1</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" orientation="portrait"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>